--- a/research/files/route_metrics.xlsx
+++ b/research/files/route_metrics.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,17 @@
       <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>How every number here is computed, and what its limits are: https://bccycletourism.ca/research/files/route_ratings_methodology.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>The research here uses AI assistance (Claude models, Anthropic) for data collection, analysis, and writing. Feel free to ask for more details if you are interested.</t>
         </is>

--- a/research/files/route_metrics.xlsx
+++ b/research/files/route_metrics.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -484,44 +484,78 @@
       <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>One row per route, 327 rows. A blank cell means we could not measure that thing, not that it is zero.</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Licence: Creative Commons Zero 1.0 Universal (CC0). We have waived our copyright in this file worldwide. Use it, change it, redistribute it, build on it, sell it. No permission needed and no conditions attached. https://creativecommons.org/publicdomain/zero/1.0/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>See the Column guide sheet for what every column holds.</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Contains information from OpenStreetMap, © OpenStreetMap contributors, available under the Open Database Licence (ODbL) 1.0. https://opendatacommons.org/licenses/odbl/1-0/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>These numbers are derived from OpenStreetMap. We do not yet record which OpenStreetMap extract produced any given number, so a route's labels can change when we rebuild, and this file cannot be exactly reproduced from a dated source. Recording the extract is planned work, not something already done.</t>
+          <t>Attribution is not legally required under CC0, but often requested as a community norm. A citation facilitates transparency and discovery, so thanks in advance!</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Suggested citation: BC Cycle Tourism Society (2026). Published BC cycling routes — derived metrics [data set]. Version 2026-07-25. https://bccycletourism.ca/research/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>How every number here is computed, and what its limits are: https://bccycletourism.ca/research/files/route_ratings_methodology.pdf</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>One row per route, 327 rows. A blank cell means we could not measure that thing, not that it is zero.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>See the Column guide sheet for what every column holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>These numbers are derived from OpenStreetMap. We do not yet record which OpenStreetMap extract produced any given number, so a route's labels can change when we rebuild, and this file cannot be exactly reproduced from a dated source. Recording the extract is planned work, not something already done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>How every number here is computed, and what its limits are: https://bccycletourism.ca/research/files/route_ratings_methodology.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>The research here uses AI assistance (Claude models, Anthropic) for data collection, analysis, and writing. Feel free to ask for more details if you are interested.</t>
         </is>

--- a/research/files/route_metrics.xlsx
+++ b/research/files/route_metrics.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Published 2026-07-25 by BC Cycle Tourism Society.</t>
+          <t>Published 2026-07-26 by BC Cycle Tourism Society.</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Suggested citation: BC Cycle Tourism Society (2026). Published BC cycling routes — derived metrics [data set]. Version 2026-07-25. https://bccycletourism.ca/research/</t>
+          <t>Suggested citation: BC Cycle Tourism Society (2026). Published BC cycling routes — derived metrics [data set]. Version 2026-07-26. https://bccycletourism.ca/research/</t>
         </is>
       </c>
     </row>
@@ -828,37 +828,37 @@
       </c>
       <c r="AY1" s="2" t="inlineStr">
         <is>
-          <t>comfort_km_most</t>
+          <t>comfort_km_c1</t>
         </is>
       </c>
       <c r="AZ1" s="2" t="inlineStr">
         <is>
-          <t>comfort_km_some</t>
+          <t>comfort_km_c2</t>
         </is>
       </c>
       <c r="BA1" s="2" t="inlineStr">
         <is>
-          <t>comfort_km_few</t>
+          <t>comfort_km_c3</t>
         </is>
       </c>
       <c r="BB1" s="2" t="inlineStr">
         <is>
-          <t>comfort_km_very_few</t>
+          <t>comfort_km_c4</t>
         </is>
       </c>
       <c r="BC1" s="2" t="inlineStr">
         <is>
+          <t>comfort_km_c5</t>
+        </is>
+      </c>
+      <c r="BD1" s="2" t="inlineStr">
+        <is>
+          <t>comfort_km_c6</t>
+        </is>
+      </c>
+      <c r="BE1" s="2" t="inlineStr">
+        <is>
           <t>comfort_km_backcountry</t>
-        </is>
-      </c>
-      <c r="BD1" s="2" t="inlineStr">
-        <is>
-          <t>comfort_km_experienced_only</t>
-        </is>
-      </c>
-      <c r="BE1" s="2" t="inlineStr">
-        <is>
-          <t>comfort_km_risk</t>
         </is>
       </c>
       <c r="BF1" s="2" t="inlineStr">
@@ -1051,13 +1051,13 @@
         <v>1.7</v>
       </c>
       <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -1257,13 +1257,13 @@
         <v>14.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>32.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>32.8</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
@@ -1463,13 +1463,13 @@
         <v>1</v>
       </c>
       <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="BE4" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>102.3</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>2</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.1</v>
+        <v>65.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>65.7</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
@@ -1862,13 +1862,13 @@
         <v>7.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>10.6</v>
+        <v>0.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
@@ -2055,13 +2055,13 @@
         <v>0</v>
       </c>
       <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
         <v>0.3</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -2261,13 +2261,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BC8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="BE8" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>46.6</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2454,10 +2454,10 @@
         <v>3</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
         <v>37.1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -2843,10 +2843,10 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>126.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>126.6</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
         <v>0</v>
@@ -3021,13 +3021,13 @@
         <v>0</v>
       </c>
       <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
         <v>3.1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>20.1</v>
       </c>
       <c r="BC13" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BE13" t="n">
         <v>38.2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>9.5</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3415,13 +3415,13 @@
         <v>0.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
-        <v>5</v>
+        <v>50.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>50.4</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3600,13 +3600,13 @@
         <v>0.4</v>
       </c>
       <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
         <v>4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3801,13 +3801,13 @@
         <v>0.4</v>
       </c>
       <c r="BC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE16" t="n">
         <v>27</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>11.5</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3993,13 +3993,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE17" t="n">
         <v>0.8</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.1</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4191,13 +4191,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BE18" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>8.699999999999999</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4577,13 +4577,13 @@
         <v>0.3</v>
       </c>
       <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
         <v>3.8</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4778,13 +4778,13 @@
         <v>30.3</v>
       </c>
       <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="BE21" t="n">
         <v>9.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>45.7</v>
       </c>
       <c r="BF21" t="n">
         <v>0</v>
@@ -4983,13 +4983,13 @@
         <v>28.5</v>
       </c>
       <c r="BC22" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="BE22" t="n">
         <v>231.3</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>107.6</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -5191,13 +5191,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="BC23" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="BE23" t="n">
         <v>45.8</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>152.8</v>
       </c>
       <c r="BF23" t="n">
         <v>0.3</v>
@@ -5396,13 +5396,13 @@
         <v>1.8</v>
       </c>
       <c r="BC24" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>160</v>
+      </c>
+      <c r="BE24" t="n">
         <v>173.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>160</v>
       </c>
       <c r="BF24" t="n">
         <v>0</v>
@@ -5597,10 +5597,10 @@
         <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
         <v>0</v>
@@ -5979,13 +5979,13 @@
         <v>0</v>
       </c>
       <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
         <v>68.90000000000001</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0</v>
       </c>
       <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
         <v>91.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6360,13 +6360,13 @@
         <v>0</v>
       </c>
       <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
         <v>83.90000000000001</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
       </c>
       <c r="BF29" t="n">
         <v>0</v>
@@ -6561,13 +6561,13 @@
         <v>3</v>
       </c>
       <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE30" t="n">
         <v>19.3</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>14.5</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.1</v>
       </c>
       <c r="BC31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
         <v>0.3</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -7329,13 +7329,13 @@
         <v>0</v>
       </c>
       <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BE34" t="n">
         <v>15.1</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0.4</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7703,13 +7703,13 @@
         <v>0.2</v>
       </c>
       <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -8077,13 +8077,13 @@
         <v>0</v>
       </c>
       <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
         <v>0.4</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0</v>
       </c>
       <c r="BF38" t="n">
         <v>0</v>
@@ -8264,10 +8264,10 @@
         <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         <v>2.9</v>
       </c>
       <c r="BC40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE40" t="n">
         <v>1.1</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>9.4</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0</v>
       </c>
       <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
         <v>0.6</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>0</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8833,13 +8833,13 @@
         <v>1.5</v>
       </c>
       <c r="BC42" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BD42" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -9408,13 +9408,13 @@
         <v>2.7</v>
       </c>
       <c r="BC45" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE45" t="n">
         <v>97.5</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>3.7</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9807,10 +9807,10 @@
         <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
         <v>0.5</v>
@@ -9983,13 +9983,13 @@
         <v>0</v>
       </c>
       <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BE48" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>0.6</v>
       </c>
       <c r="BF48" t="n">
         <v>0</v>
@@ -10179,13 +10179,13 @@
         <v>3.5</v>
       </c>
       <c r="BC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" t="n">
         <v>2.5</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>0</v>
       </c>
       <c r="BF49" t="n">
         <v>0</v>
@@ -10380,13 +10380,13 @@
         <v>5.7</v>
       </c>
       <c r="BC50" t="n">
+        <v>33</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE50" t="n">
         <v>279.4</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>33</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>7.8</v>
       </c>
       <c r="BF50" t="n">
         <v>0</v>
@@ -10573,13 +10573,13 @@
         <v>0.2</v>
       </c>
       <c r="BC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE51" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>0</v>
       </c>
       <c r="BF51" t="n">
         <v>0</v>
@@ -10769,13 +10769,13 @@
         <v>8.300000000000001</v>
       </c>
       <c r="BC52" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0</v>
       </c>
       <c r="BF52" t="n">
         <v>0</v>
@@ -10972,13 +10972,13 @@
         <v>8.9</v>
       </c>
       <c r="BC53" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>983.3</v>
+      </c>
+      <c r="BE53" t="n">
         <v>2.2</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>983.3</v>
       </c>
       <c r="BF53" t="n">
         <v>0</v>
@@ -11170,13 +11170,13 @@
         <v>3.6</v>
       </c>
       <c r="BC54" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>461.6</v>
+      </c>
+      <c r="BE54" t="n">
         <v>3.5</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE54" t="n">
-        <v>461.6</v>
       </c>
       <c r="BF54" t="n">
         <v>2.9</v>
@@ -11360,13 +11360,13 @@
         <v>26.5</v>
       </c>
       <c r="BC55" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="BE55" t="n">
         <v>0.4</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>16.1</v>
       </c>
       <c r="BF55" t="n">
         <v>0.6</v>
@@ -11539,13 +11539,13 @@
         <v>0.1</v>
       </c>
       <c r="BC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE56" t="n">
         <v>3.6</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>0</v>
       </c>
       <c r="BF56" t="n">
         <v>0</v>
@@ -11720,13 +11720,13 @@
         <v>9.1</v>
       </c>
       <c r="BC57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE57" t="n">
         <v>3.2</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>0</v>
       </c>
       <c r="BF57" t="n">
         <v>0</v>
@@ -11901,13 +11901,13 @@
         <v>2.9</v>
       </c>
       <c r="BC58" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE58" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BD58" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BE58" t="n">
-        <v>0</v>
       </c>
       <c r="BF58" t="n">
         <v>0</v>
@@ -12094,13 +12094,13 @@
         <v>0</v>
       </c>
       <c r="BC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE59" t="n">
         <v>1.7</v>
-      </c>
-      <c r="BD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE59" t="n">
-        <v>0</v>
       </c>
       <c r="BF59" t="n">
         <v>0</v>
@@ -12287,13 +12287,13 @@
         <v>0</v>
       </c>
       <c r="BC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE60" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE60" t="n">
-        <v>0</v>
       </c>
       <c r="BF60" t="n">
         <v>0</v>
@@ -12480,13 +12480,13 @@
         <v>1.6</v>
       </c>
       <c r="BC61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BE61" t="n">
         <v>3.2</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>1.2</v>
       </c>
       <c r="BF61" t="n">
         <v>0.1</v>
@@ -12661,13 +12661,13 @@
         <v>1</v>
       </c>
       <c r="BC62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE62" t="n">
         <v>2.2</v>
-      </c>
-      <c r="BD62" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BE62" t="n">
-        <v>0</v>
       </c>
       <c r="BF62" t="n">
         <v>0.1</v>
@@ -13024,13 +13024,13 @@
         <v>0</v>
       </c>
       <c r="BC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE64" t="n">
         <v>3.1</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE64" t="n">
-        <v>0</v>
       </c>
       <c r="BF64" t="n">
         <v>0</v>
@@ -13230,13 +13230,13 @@
         <v>6.1</v>
       </c>
       <c r="BC65" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="BE65" t="n">
         <v>0.3</v>
-      </c>
-      <c r="BD65" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="BE65" t="n">
-        <v>23.6</v>
       </c>
       <c r="BF65" t="n">
         <v>0</v>
@@ -13416,13 +13416,13 @@
         <v>9.699999999999999</v>
       </c>
       <c r="BC66" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="BE66" t="n">
         <v>112.6</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>62.2</v>
       </c>
       <c r="BF66" t="n">
         <v>0</v>
@@ -13612,13 +13612,13 @@
         <v>0.5</v>
       </c>
       <c r="BC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE67" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE67" t="n">
-        <v>0</v>
       </c>
       <c r="BF67" t="n">
         <v>0</v>
@@ -13805,13 +13805,13 @@
         <v>4.3</v>
       </c>
       <c r="BC68" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE68" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE68" t="n">
-        <v>1.1</v>
       </c>
       <c r="BF68" t="n">
         <v>0</v>
@@ -14003,13 +14003,13 @@
         <v>0</v>
       </c>
       <c r="BC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE69" t="n">
         <v>20.1</v>
-      </c>
-      <c r="BD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE69" t="n">
-        <v>2.5</v>
       </c>
       <c r="BF69" t="n">
         <v>0</v>
@@ -14198,13 +14198,13 @@
         <v>6.7</v>
       </c>
       <c r="BC70" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE70" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BD70" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="BE70" t="n">
-        <v>1.3</v>
       </c>
       <c r="BF70" t="n">
         <v>0</v>
@@ -14389,13 +14389,13 @@
         <v>0</v>
       </c>
       <c r="BC71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="BE71" t="n">
         <v>28.3</v>
-      </c>
-      <c r="BD71" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE71" t="n">
-        <v>63.9</v>
       </c>
       <c r="BF71" t="n">
         <v>0</v>
@@ -14582,13 +14582,13 @@
         <v>0</v>
       </c>
       <c r="BC72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD72" t="n">
         <v>0</v>
       </c>
       <c r="BE72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF72" t="n">
         <v>0</v>
@@ -14774,13 +14774,13 @@
         <v>1</v>
       </c>
       <c r="BC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE73" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BD73" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE73" t="n">
-        <v>0</v>
       </c>
       <c r="BF73" t="n">
         <v>0</v>
@@ -14967,13 +14967,13 @@
         <v>0</v>
       </c>
       <c r="BC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE74" t="n">
         <v>0.3</v>
-      </c>
-      <c r="BD74" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE74" t="n">
-        <v>0</v>
       </c>
       <c r="BF74" t="n">
         <v>0</v>
@@ -15151,13 +15151,13 @@
         <v>0</v>
       </c>
       <c r="BC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE75" t="n">
         <v>0.6</v>
-      </c>
-      <c r="BD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE75" t="n">
-        <v>0</v>
       </c>
       <c r="BF75" t="n">
         <v>0</v>
@@ -15347,13 +15347,13 @@
         <v>2.1</v>
       </c>
       <c r="BC76" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BE76" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD76" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BE76" t="n">
-        <v>0.5</v>
       </c>
       <c r="BF76" t="n">
         <v>0</v>
@@ -15545,13 +15545,13 @@
         <v>7.6</v>
       </c>
       <c r="BC77" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE77" t="n">
         <v>1.7</v>
-      </c>
-      <c r="BD77" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="BE77" t="n">
-        <v>0.2</v>
       </c>
       <c r="BF77" t="n">
         <v>0</v>
@@ -15748,13 +15748,13 @@
         <v>9.5</v>
       </c>
       <c r="BC78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE78" t="n">
         <v>0.3</v>
-      </c>
-      <c r="BD78" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="BE78" t="n">
-        <v>2.6</v>
       </c>
       <c r="BF78" t="n">
         <v>0</v>
@@ -15946,10 +15946,10 @@
         <v>6.6</v>
       </c>
       <c r="BC79" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BD79" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -16144,10 +16144,10 @@
         <v>6.6</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="BD80" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -16342,13 +16342,13 @@
         <v>6</v>
       </c>
       <c r="BC81" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE81" t="n">
         <v>3.6</v>
-      </c>
-      <c r="BD81" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="BE81" t="n">
-        <v>0.3</v>
       </c>
       <c r="BF81" t="n">
         <v>0</v>
@@ -16545,13 +16545,13 @@
         <v>7.9</v>
       </c>
       <c r="BC82" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE82" t="n">
         <v>2.2</v>
-      </c>
-      <c r="BD82" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="BE82" t="n">
-        <v>2.7</v>
       </c>
       <c r="BF82" t="n">
         <v>0</v>
@@ -16738,13 +16738,13 @@
         <v>0</v>
       </c>
       <c r="BC83" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE83" t="n">
         <v>3</v>
-      </c>
-      <c r="BD83" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE83" t="n">
-        <v>0</v>
       </c>
       <c r="BF83" t="n">
         <v>0</v>
@@ -16931,13 +16931,13 @@
         <v>0</v>
       </c>
       <c r="BC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE84" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BD84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE84" t="n">
-        <v>0</v>
       </c>
       <c r="BF84" t="n">
         <v>0</v>
@@ -17124,13 +17124,13 @@
         <v>0</v>
       </c>
       <c r="BC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE85" t="n">
         <v>6</v>
-      </c>
-      <c r="BD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE85" t="n">
-        <v>0</v>
       </c>
       <c r="BF85" t="n">
         <v>0</v>
@@ -17317,13 +17317,13 @@
         <v>0.3</v>
       </c>
       <c r="BC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE86" t="n">
         <v>2.1</v>
-      </c>
-      <c r="BD86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE86" t="n">
-        <v>0.2</v>
       </c>
       <c r="BF86" t="n">
         <v>0</v>
@@ -17510,13 +17510,13 @@
         <v>0.2</v>
       </c>
       <c r="BC87" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE87" t="n">
         <v>3.1</v>
-      </c>
-      <c r="BD87" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BE87" t="n">
-        <v>0</v>
       </c>
       <c r="BF87" t="n">
         <v>0</v>
@@ -17703,13 +17703,13 @@
         <v>0</v>
       </c>
       <c r="BC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE88" t="n">
         <v>2</v>
-      </c>
-      <c r="BD88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE88" t="n">
-        <v>0</v>
       </c>
       <c r="BF88" t="n">
         <v>0</v>
@@ -17896,13 +17896,13 @@
         <v>0.7</v>
       </c>
       <c r="BC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE89" t="n">
         <v>1.5</v>
-      </c>
-      <c r="BD89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE89" t="n">
-        <v>0</v>
       </c>
       <c r="BF89" t="n">
         <v>0</v>
@@ -18089,13 +18089,13 @@
         <v>0</v>
       </c>
       <c r="BC90" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE90" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BD90" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BE90" t="n">
-        <v>0</v>
       </c>
       <c r="BF90" t="n">
         <v>0</v>
@@ -18282,13 +18282,13 @@
         <v>0</v>
       </c>
       <c r="BC91" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE91" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BD91" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BE91" t="n">
-        <v>0</v>
       </c>
       <c r="BF91" t="n">
         <v>0</v>
@@ -18475,13 +18475,13 @@
         <v>0.4</v>
       </c>
       <c r="BC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE92" t="n">
         <v>2.1</v>
-      </c>
-      <c r="BD92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE92" t="n">
-        <v>0</v>
       </c>
       <c r="BF92" t="n">
         <v>0</v>
@@ -18673,13 +18673,13 @@
         <v>8.9</v>
       </c>
       <c r="BC93" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE93" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD93" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="BE93" t="n">
-        <v>3.1</v>
       </c>
       <c r="BF93" t="n">
         <v>0</v>
@@ -18871,10 +18871,10 @@
         <v>10.9</v>
       </c>
       <c r="BC94" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BD94" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BE94" t="n">
         <v>0</v>
@@ -19064,13 +19064,13 @@
         <v>0</v>
       </c>
       <c r="BC95" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE95" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BD95" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE95" t="n">
-        <v>0</v>
       </c>
       <c r="BF95" t="n">
         <v>0</v>
@@ -19262,13 +19262,13 @@
         <v>16.4</v>
       </c>
       <c r="BC96" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE96" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BD96" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BE96" t="n">
-        <v>0</v>
       </c>
       <c r="BF96" t="n">
         <v>0</v>
@@ -19460,13 +19460,13 @@
         <v>3.7</v>
       </c>
       <c r="BC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="BE97" t="n">
         <v>21.1</v>
-      </c>
-      <c r="BD97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE97" t="n">
-        <v>15.9</v>
       </c>
       <c r="BF97" t="n">
         <v>0</v>
@@ -19658,10 +19658,10 @@
         <v>6.7</v>
       </c>
       <c r="BC98" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BD98" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="BE98" t="n">
         <v>0</v>
@@ -19856,13 +19856,13 @@
         <v>5.2</v>
       </c>
       <c r="BC99" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE99" t="n">
         <v>5</v>
-      </c>
-      <c r="BD99" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BE99" t="n">
-        <v>6.4</v>
       </c>
       <c r="BF99" t="n">
         <v>0</v>
@@ -20049,10 +20049,10 @@
         <v>3.2</v>
       </c>
       <c r="BC100" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BD100" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -20242,13 +20242,13 @@
         <v>0.7</v>
       </c>
       <c r="BC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE101" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD101" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE101" t="n">
-        <v>0</v>
       </c>
       <c r="BF101" t="n">
         <v>0</v>
@@ -20423,13 +20423,13 @@
         <v>3.7</v>
       </c>
       <c r="BC102" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE102" t="n">
         <v>2.1</v>
-      </c>
-      <c r="BD102" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BE102" t="n">
-        <v>0</v>
       </c>
       <c r="BF102" t="n">
         <v>0</v>
@@ -20627,10 +20627,10 @@
         <v>0</v>
       </c>
       <c r="BD103" t="n">
-        <v>0</v>
+        <v>101.4</v>
       </c>
       <c r="BE103" t="n">
-        <v>101.4</v>
+        <v>0</v>
       </c>
       <c r="BF103" t="n">
         <v>0</v>
@@ -20820,10 +20820,10 @@
         <v>0</v>
       </c>
       <c r="BD104" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BE104" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BF104" t="n">
         <v>0</v>
@@ -21015,13 +21015,13 @@
         <v>2.1</v>
       </c>
       <c r="BC105" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="BE105" t="n">
         <v>0.3</v>
-      </c>
-      <c r="BD105" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="BE105" t="n">
-        <v>17.1</v>
       </c>
       <c r="BF105" t="n">
         <v>0</v>
@@ -21208,13 +21208,13 @@
         <v>1.4</v>
       </c>
       <c r="BC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE106" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BD106" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE106" t="n">
-        <v>0</v>
       </c>
       <c r="BF106" t="n">
         <v>0.2</v>
@@ -21406,13 +21406,13 @@
         <v>3.7</v>
       </c>
       <c r="BC107" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE107" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BD107" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE107" t="n">
-        <v>5.1</v>
       </c>
       <c r="BF107" t="n">
         <v>0.2</v>
@@ -21612,13 +21612,13 @@
         <v>0.2</v>
       </c>
       <c r="BC108" t="n">
-        <v>0</v>
+        <v>63.8</v>
       </c>
       <c r="BD108" t="n">
-        <v>63.8</v>
+        <v>69.7</v>
       </c>
       <c r="BE108" t="n">
-        <v>69.7</v>
+        <v>0</v>
       </c>
       <c r="BF108" t="n">
         <v>0</v>
@@ -21799,13 +21799,13 @@
         <v>0.1</v>
       </c>
       <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE109" t="n">
         <v>0.7</v>
-      </c>
-      <c r="BD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE109" t="n">
-        <v>0</v>
       </c>
       <c r="BF109" t="n">
         <v>0</v>
@@ -21994,13 +21994,13 @@
         <v>0.2</v>
       </c>
       <c r="BC110" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="BE110" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD110" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE110" t="n">
-        <v>49.2</v>
       </c>
       <c r="BF110" t="n">
         <v>0</v>
@@ -22197,13 +22197,13 @@
         <v>3</v>
       </c>
       <c r="BC111" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>232</v>
+      </c>
+      <c r="BE111" t="n">
         <v>1.4</v>
-      </c>
-      <c r="BD111" t="n">
-        <v>123.1</v>
-      </c>
-      <c r="BE111" t="n">
-        <v>232</v>
       </c>
       <c r="BF111" t="n">
         <v>0</v>
@@ -22786,13 +22786,13 @@
         <v>0</v>
       </c>
       <c r="BC114" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="BE114" t="n">
         <v>15</v>
-      </c>
-      <c r="BD114" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="BE114" t="n">
-        <v>202.6</v>
       </c>
       <c r="BF114" t="n">
         <v>0</v>
@@ -23363,13 +23363,13 @@
         <v>10.7</v>
       </c>
       <c r="BC117" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="BE117" t="n">
         <v>15.4</v>
-      </c>
-      <c r="BD117" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="BE117" t="n">
-        <v>57.7</v>
       </c>
       <c r="BF117" t="n">
         <v>0</v>
@@ -23542,13 +23542,13 @@
         <v>9.699999999999999</v>
       </c>
       <c r="BC118" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE118" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BD118" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BE118" t="n">
-        <v>0</v>
       </c>
       <c r="BF118" t="n">
         <v>0</v>
@@ -23726,13 +23726,13 @@
         <v>1.1</v>
       </c>
       <c r="BC119" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE119" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD119" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="BE119" t="n">
-        <v>4.3</v>
       </c>
       <c r="BF119" t="n">
         <v>0</v>
@@ -23916,10 +23916,10 @@
         <v>0</v>
       </c>
       <c r="BD120" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE120" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BF120" t="n">
         <v>0</v>
@@ -24089,13 +24089,13 @@
         <v>0</v>
       </c>
       <c r="BC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE121" t="n">
         <v>0.3</v>
-      </c>
-      <c r="BD121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE121" t="n">
-        <v>0</v>
       </c>
       <c r="BF121" t="n">
         <v>0</v>
@@ -24450,13 +24450,13 @@
         <v>0</v>
       </c>
       <c r="BC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE123" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE123" t="n">
-        <v>0</v>
       </c>
       <c r="BF123" t="n">
         <v>0</v>
@@ -24622,13 +24622,13 @@
         <v>0</v>
       </c>
       <c r="BC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE124" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE124" t="n">
-        <v>0</v>
       </c>
       <c r="BF124" t="n">
         <v>0</v>
@@ -24801,13 +24801,13 @@
         <v>9.300000000000001</v>
       </c>
       <c r="BC125" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE125" t="n">
         <v>1.1</v>
-      </c>
-      <c r="BD125" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="BE125" t="n">
-        <v>1.4</v>
       </c>
       <c r="BF125" t="n">
         <v>0</v>
@@ -24985,13 +24985,13 @@
         <v>12</v>
       </c>
       <c r="BC126" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="BD126" t="n">
-        <v>22.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE126" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BF126" t="n">
         <v>0</v>
@@ -25164,13 +25164,13 @@
         <v>2.4</v>
       </c>
       <c r="BC127" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE127" t="n">
         <v>8</v>
-      </c>
-      <c r="BD127" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BE127" t="n">
-        <v>0</v>
       </c>
       <c r="BF127" t="n">
         <v>0</v>
@@ -25527,13 +25527,13 @@
         <v>6.1</v>
       </c>
       <c r="BC129" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE129" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD129" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="BE129" t="n">
-        <v>0</v>
       </c>
       <c r="BF129" t="n">
         <v>0</v>
@@ -25706,13 +25706,13 @@
         <v>0.9</v>
       </c>
       <c r="BC130" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD130" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="BE130" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="BF130" t="n">
         <v>0</v>
@@ -25890,13 +25890,13 @@
         <v>21</v>
       </c>
       <c r="BC131" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BE131" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BD131" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="BE131" t="n">
-        <v>6.3</v>
       </c>
       <c r="BF131" t="n">
         <v>0</v>
@@ -26069,13 +26069,13 @@
         <v>6.7</v>
       </c>
       <c r="BC132" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BE132" t="n">
         <v>2.6</v>
-      </c>
-      <c r="BD132" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BE132" t="n">
-        <v>0.1</v>
       </c>
       <c r="BF132" t="n">
         <v>0</v>
@@ -26248,13 +26248,13 @@
         <v>0</v>
       </c>
       <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE133" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE133" t="n">
-        <v>0</v>
       </c>
       <c r="BF133" t="n">
         <v>0</v>
@@ -26427,13 +26427,13 @@
         <v>5.2</v>
       </c>
       <c r="BC134" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE134" t="n">
         <v>0.4</v>
-      </c>
-      <c r="BD134" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BE134" t="n">
-        <v>0</v>
       </c>
       <c r="BF134" t="n">
         <v>0</v>
@@ -26611,13 +26611,13 @@
         <v>1.7</v>
       </c>
       <c r="BC135" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE135" t="n">
         <v>3.3</v>
-      </c>
-      <c r="BD135" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BE135" t="n">
-        <v>5.2</v>
       </c>
       <c r="BF135" t="n">
         <v>0</v>
@@ -26790,10 +26790,10 @@
         <v>2.9</v>
       </c>
       <c r="BC136" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BD136" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BE136" t="n">
         <v>0</v>
@@ -26969,13 +26969,13 @@
         <v>1.2</v>
       </c>
       <c r="BC137" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE137" t="n">
         <v>0.6</v>
-      </c>
-      <c r="BD137" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE137" t="n">
-        <v>0.2</v>
       </c>
       <c r="BF137" t="n">
         <v>0</v>
@@ -27332,13 +27332,13 @@
         <v>0.3</v>
       </c>
       <c r="BC139" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE139" t="n">
         <v>10.8</v>
-      </c>
-      <c r="BD139" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE139" t="n">
-        <v>12.5</v>
       </c>
       <c r="BF139" t="n">
         <v>0</v>
@@ -27514,13 +27514,13 @@
         <v>0</v>
       </c>
       <c r="BC140" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BE140" t="n">
         <v>7.7</v>
-      </c>
-      <c r="BD140" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE140" t="n">
-        <v>0.1</v>
       </c>
       <c r="BF140" t="n">
         <v>0</v>
@@ -27698,13 +27698,13 @@
         <v>0.2</v>
       </c>
       <c r="BC141" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE141" t="n">
         <v>6.1</v>
-      </c>
-      <c r="BD141" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BE141" t="n">
-        <v>2.1</v>
       </c>
       <c r="BF141" t="n">
         <v>0</v>
@@ -27885,13 +27885,13 @@
         <v>0.5</v>
       </c>
       <c r="BC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE142" t="n">
         <v>0.7</v>
-      </c>
-      <c r="BD142" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE142" t="n">
-        <v>2.3</v>
       </c>
       <c r="BF142" t="n">
         <v>0</v>
@@ -28077,13 +28077,13 @@
         <v>14</v>
       </c>
       <c r="BC143" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="BE143" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BD143" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BE143" t="n">
-        <v>56.1</v>
       </c>
       <c r="BF143" t="n">
         <v>0</v>
@@ -28256,13 +28256,13 @@
         <v>0</v>
       </c>
       <c r="BC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE144" t="n">
         <v>10.2</v>
-      </c>
-      <c r="BD144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE144" t="n">
-        <v>0</v>
       </c>
       <c r="BF144" t="n">
         <v>0</v>
@@ -28435,13 +28435,13 @@
         <v>0</v>
       </c>
       <c r="BC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE145" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE145" t="n">
-        <v>0</v>
       </c>
       <c r="BF145" t="n">
         <v>0</v>
@@ -28619,13 +28619,13 @@
         <v>12.2</v>
       </c>
       <c r="BC146" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE146" t="n">
         <v>11.9</v>
-      </c>
-      <c r="BD146" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="BE146" t="n">
-        <v>5</v>
       </c>
       <c r="BF146" t="n">
         <v>0</v>
@@ -28803,13 +28803,13 @@
         <v>2.4</v>
       </c>
       <c r="BC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="BE147" t="n">
         <v>10.4</v>
-      </c>
-      <c r="BD147" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE147" t="n">
-        <v>12.2</v>
       </c>
       <c r="BF147" t="n">
         <v>0</v>
@@ -28987,13 +28987,13 @@
         <v>6.2</v>
       </c>
       <c r="BC148" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE148" t="n">
         <v>6.3</v>
-      </c>
-      <c r="BD148" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE148" t="n">
-        <v>3.3</v>
       </c>
       <c r="BF148" t="n">
         <v>0</v>
@@ -29358,13 +29358,13 @@
         <v>5</v>
       </c>
       <c r="BC150" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE150" t="n">
         <v>1.6</v>
-      </c>
-      <c r="BD150" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BE150" t="n">
-        <v>13.5</v>
       </c>
       <c r="BF150" t="n">
         <v>0</v>
@@ -29542,13 +29542,13 @@
         <v>2.3</v>
       </c>
       <c r="BC151" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="BE151" t="n">
         <v>2.8</v>
-      </c>
-      <c r="BD151" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BE151" t="n">
-        <v>14.9</v>
       </c>
       <c r="BF151" t="n">
         <v>0</v>
@@ -29721,13 +29721,13 @@
         <v>2.8</v>
       </c>
       <c r="BC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BE152" t="n">
         <v>1.5</v>
-      </c>
-      <c r="BD152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE152" t="n">
-        <v>1.2</v>
       </c>
       <c r="BF152" t="n">
         <v>0</v>
@@ -30079,13 +30079,13 @@
         <v>2.7</v>
       </c>
       <c r="BC154" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE154" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BD154" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE154" t="n">
-        <v>0</v>
       </c>
       <c r="BF154" t="n">
         <v>0</v>
@@ -30263,13 +30263,13 @@
         <v>2.5</v>
       </c>
       <c r="BC155" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE155" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BD155" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="BE155" t="n">
-        <v>0</v>
       </c>
       <c r="BF155" t="n">
         <v>0</v>
@@ -30450,13 +30450,13 @@
         <v>0</v>
       </c>
       <c r="BC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="BE156" t="n">
         <v>2.2</v>
-      </c>
-      <c r="BD156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE156" t="n">
-        <v>25.9</v>
       </c>
       <c r="BF156" t="n">
         <v>0</v>
@@ -30634,13 +30634,13 @@
         <v>0</v>
       </c>
       <c r="BC157" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE157" t="n">
         <v>3.6</v>
-      </c>
-      <c r="BD157" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BE157" t="n">
-        <v>11.5</v>
       </c>
       <c r="BF157" t="n">
         <v>0</v>
@@ -30818,13 +30818,13 @@
         <v>0</v>
       </c>
       <c r="BC158" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE158" t="n">
         <v>3.5</v>
-      </c>
-      <c r="BD158" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BE158" t="n">
-        <v>3.7</v>
       </c>
       <c r="BF158" t="n">
         <v>0</v>
@@ -30997,13 +30997,13 @@
         <v>0</v>
       </c>
       <c r="BC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE159" t="n">
         <v>2.2</v>
-      </c>
-      <c r="BD159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE159" t="n">
-        <v>0</v>
       </c>
       <c r="BF159" t="n">
         <v>0</v>
@@ -31176,13 +31176,13 @@
         <v>9.4</v>
       </c>
       <c r="BC160" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE160" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BD160" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BE160" t="n">
-        <v>0</v>
       </c>
       <c r="BF160" t="n">
         <v>0</v>
@@ -31289,13 +31289,13 @@
         <v>0</v>
       </c>
       <c r="BC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE161" t="n">
         <v>0.7</v>
-      </c>
-      <c r="BD161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE161" t="n">
-        <v>0</v>
       </c>
       <c r="BF161" t="n">
         <v>0</v>
@@ -31473,13 +31473,13 @@
         <v>0</v>
       </c>
       <c r="BC162" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="BE162" t="n">
         <v>108.7</v>
-      </c>
-      <c r="BD162" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE162" t="n">
-        <v>34.3</v>
       </c>
       <c r="BF162" t="n">
         <v>0</v>
@@ -31652,13 +31652,13 @@
         <v>0</v>
       </c>
       <c r="BC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE163" t="n">
         <v>22.9</v>
-      </c>
-      <c r="BD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE163" t="n">
-        <v>1.3</v>
       </c>
       <c r="BF163" t="n">
         <v>0</v>
@@ -31831,13 +31831,13 @@
         <v>0.1</v>
       </c>
       <c r="BC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE164" t="n">
         <v>3.7</v>
-      </c>
-      <c r="BD164" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE164" t="n">
-        <v>0.3</v>
       </c>
       <c r="BF164" t="n">
         <v>0</v>
@@ -32015,13 +32015,13 @@
         <v>0</v>
       </c>
       <c r="BC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BE165" t="n">
         <v>38.7</v>
-      </c>
-      <c r="BD165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE165" t="n">
-        <v>24.5</v>
       </c>
       <c r="BF165" t="n">
         <v>0</v>
@@ -32194,13 +32194,13 @@
         <v>0.4</v>
       </c>
       <c r="BC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE166" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BD166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE166" t="n">
-        <v>0</v>
       </c>
       <c r="BF166" t="n">
         <v>0</v>
@@ -32378,13 +32378,13 @@
         <v>0.1</v>
       </c>
       <c r="BC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE167" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BD167" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE167" t="n">
-        <v>4.9</v>
       </c>
       <c r="BF167" t="n">
         <v>0</v>
@@ -32562,13 +32562,13 @@
         <v>0.7</v>
       </c>
       <c r="BC168" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE168" t="n">
         <v>3.8</v>
-      </c>
-      <c r="BD168" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE168" t="n">
-        <v>5.7</v>
       </c>
       <c r="BF168" t="n">
         <v>0</v>
@@ -32741,13 +32741,13 @@
         <v>0</v>
       </c>
       <c r="BC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE169" t="n">
         <v>3.8</v>
-      </c>
-      <c r="BD169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE169" t="n">
-        <v>0</v>
       </c>
       <c r="BF169" t="n">
         <v>0</v>
@@ -32920,13 +32920,13 @@
         <v>0</v>
       </c>
       <c r="BC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE170" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BD170" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE170" t="n">
-        <v>0</v>
       </c>
       <c r="BF170" t="n">
         <v>0</v>
@@ -33099,13 +33099,13 @@
         <v>2.4</v>
       </c>
       <c r="BC171" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE171" t="n">
         <v>8</v>
-      </c>
-      <c r="BD171" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BE171" t="n">
-        <v>0</v>
       </c>
       <c r="BF171" t="n">
         <v>0</v>
@@ -33286,10 +33286,10 @@
         <v>0</v>
       </c>
       <c r="BD172" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BE172" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BF172" t="n">
         <v>0</v>
@@ -33462,13 +33462,13 @@
         <v>11.7</v>
       </c>
       <c r="BC173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE173" t="n">
         <v>2.2</v>
-      </c>
-      <c r="BD173" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE173" t="n">
-        <v>0.3</v>
       </c>
       <c r="BF173" t="n">
         <v>0</v>
@@ -33658,13 +33658,13 @@
         <v>0</v>
       </c>
       <c r="BC174" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE174" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD174" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE174" t="n">
-        <v>1.3</v>
       </c>
       <c r="BF174" t="n">
         <v>0</v>
@@ -33856,13 +33856,13 @@
         <v>1.1</v>
       </c>
       <c r="BC175" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="BE175" t="n">
         <v>10.3</v>
-      </c>
-      <c r="BD175" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BE175" t="n">
-        <v>29.6</v>
       </c>
       <c r="BF175" t="n">
         <v>0</v>
@@ -34047,13 +34047,13 @@
         <v>0.8</v>
       </c>
       <c r="BC176" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="BE176" t="n">
         <v>35.4</v>
-      </c>
-      <c r="BD176" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE176" t="n">
-        <v>58.2</v>
       </c>
       <c r="BF176" t="n">
         <v>0</v>
@@ -34248,13 +34248,13 @@
         <v>8</v>
       </c>
       <c r="BC177" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="BE177" t="n">
         <v>30.7</v>
-      </c>
-      <c r="BD177" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE177" t="n">
-        <v>46.2</v>
       </c>
       <c r="BF177" t="n">
         <v>0</v>
@@ -34439,13 +34439,13 @@
         <v>3.1</v>
       </c>
       <c r="BC178" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="BE178" t="n">
         <v>7.9</v>
-      </c>
-      <c r="BD178" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="BE178" t="n">
-        <v>54.4</v>
       </c>
       <c r="BF178" t="n">
         <v>0</v>
@@ -34628,13 +34628,13 @@
         <v>0</v>
       </c>
       <c r="BC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE179" t="n">
         <v>13.9</v>
-      </c>
-      <c r="BD179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE179" t="n">
-        <v>0</v>
       </c>
       <c r="BF179" t="n">
         <v>0</v>
@@ -34829,13 +34829,13 @@
         <v>0.2</v>
       </c>
       <c r="BC180" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BD180" t="n">
-        <v>9.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE180" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BF180" t="n">
         <v>0</v>
@@ -35022,13 +35022,13 @@
         <v>0.6</v>
       </c>
       <c r="BC181" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE181" t="n">
         <v>0.4</v>
-      </c>
-      <c r="BD181" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BE181" t="n">
-        <v>0</v>
       </c>
       <c r="BF181" t="n">
         <v>0</v>
@@ -35216,13 +35216,13 @@
         <v>0.6</v>
       </c>
       <c r="BC182" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="BE182" t="n">
         <v>23</v>
-      </c>
-      <c r="BD182" t="n">
-        <v>129.3</v>
-      </c>
-      <c r="BE182" t="n">
-        <v>163.8</v>
       </c>
       <c r="BF182" t="n">
         <v>0</v>
@@ -35412,13 +35412,13 @@
         <v>0</v>
       </c>
       <c r="BC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE183" t="n">
         <v>19.5</v>
-      </c>
-      <c r="BD183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE183" t="n">
-        <v>0</v>
       </c>
       <c r="BF183" t="n">
         <v>0</v>
@@ -35610,13 +35610,13 @@
         <v>5.8</v>
       </c>
       <c r="BC184" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="BE184" t="n">
         <v>2.2</v>
-      </c>
-      <c r="BD184" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="BE184" t="n">
-        <v>117.1</v>
       </c>
       <c r="BF184" t="n">
         <v>0</v>
@@ -35789,13 +35789,13 @@
         <v>0</v>
       </c>
       <c r="BC185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE185" t="n">
         <v>3.5</v>
-      </c>
-      <c r="BD185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE185" t="n">
-        <v>0</v>
       </c>
       <c r="BF185" t="n">
         <v>0</v>
@@ -35975,13 +35975,13 @@
         <v>1</v>
       </c>
       <c r="BC186" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE186" t="n">
         <v>10.7</v>
-      </c>
-      <c r="BD186" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BE186" t="n">
-        <v>2.5</v>
       </c>
       <c r="BF186" t="n">
         <v>0</v>
@@ -36156,13 +36156,13 @@
         <v>12.5</v>
       </c>
       <c r="BC187" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE187" t="n">
         <v>28.4</v>
-      </c>
-      <c r="BD187" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE187" t="n">
-        <v>1.3</v>
       </c>
       <c r="BF187" t="n">
         <v>0</v>
@@ -36337,13 +36337,13 @@
         <v>1.6</v>
       </c>
       <c r="BC188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE188" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BD188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE188" t="n">
-        <v>0</v>
       </c>
       <c r="BF188" t="n">
         <v>0</v>
@@ -36533,13 +36533,13 @@
         <v>1.5</v>
       </c>
       <c r="BC189" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE189" t="n">
         <v>57.2</v>
-      </c>
-      <c r="BD189" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BE189" t="n">
-        <v>1.7</v>
       </c>
       <c r="BF189" t="n">
         <v>0</v>
@@ -36929,13 +36929,13 @@
         <v>7.1</v>
       </c>
       <c r="BC191" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="BE191" t="n">
         <v>1.1</v>
-      </c>
-      <c r="BD191" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="BE191" t="n">
-        <v>14.7</v>
       </c>
       <c r="BF191" t="n">
         <v>0</v>
@@ -37122,13 +37122,13 @@
         <v>0.4</v>
       </c>
       <c r="BC192" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE192" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BD192" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BE192" t="n">
-        <v>0</v>
       </c>
       <c r="BF192" t="n">
         <v>0</v>
@@ -37320,13 +37320,13 @@
         <v>1.7</v>
       </c>
       <c r="BC193" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE193" t="n">
         <v>8.5</v>
-      </c>
-      <c r="BD193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE193" t="n">
-        <v>0</v>
       </c>
       <c r="BF193" t="n">
         <v>0.4</v>
@@ -37518,13 +37518,13 @@
         <v>11.9</v>
       </c>
       <c r="BC194" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BE194" t="n">
         <v>0.4</v>
-      </c>
-      <c r="BD194" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="BE194" t="n">
-        <v>0.1</v>
       </c>
       <c r="BF194" t="n">
         <v>0</v>
@@ -37711,13 +37711,13 @@
         <v>0</v>
       </c>
       <c r="BC195" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE195" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE195" t="n">
-        <v>0</v>
       </c>
       <c r="BF195" t="n">
         <v>0</v>
@@ -37904,13 +37904,13 @@
         <v>0</v>
       </c>
       <c r="BC196" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE196" t="n">
         <v>0.9</v>
-      </c>
-      <c r="BD196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE196" t="n">
-        <v>0</v>
       </c>
       <c r="BF196" t="n">
         <v>0</v>
@@ -38097,13 +38097,13 @@
         <v>0</v>
       </c>
       <c r="BC197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE197" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE197" t="n">
-        <v>0</v>
       </c>
       <c r="BF197" t="n">
         <v>0</v>
@@ -38282,13 +38282,13 @@
         <v>1.6</v>
       </c>
       <c r="BC198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BE198" t="n">
         <v>0.3</v>
-      </c>
-      <c r="BD198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE198" t="n">
-        <v>0.6</v>
       </c>
       <c r="BF198" t="n">
         <v>0</v>
@@ -38471,13 +38471,13 @@
         <v>1.5</v>
       </c>
       <c r="BC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BE199" t="n">
         <v>6.9</v>
-      </c>
-      <c r="BD199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE199" t="n">
-        <v>0.8</v>
       </c>
       <c r="BF199" t="n">
         <v>0</v>
@@ -39231,13 +39231,13 @@
         <v>0.3</v>
       </c>
       <c r="BC203" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE203" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BD203" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BE203" t="n">
-        <v>0</v>
       </c>
       <c r="BF203" t="n">
         <v>0</v>
@@ -39415,13 +39415,13 @@
         <v>0.2</v>
       </c>
       <c r="BC204" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="BD204" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE204" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BF204" t="n">
         <v>0</v>
@@ -39599,13 +39599,13 @@
         <v>2.8</v>
       </c>
       <c r="BC205" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE205" t="n">
         <v>71.5</v>
-      </c>
-      <c r="BD205" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BE205" t="n">
-        <v>24</v>
       </c>
       <c r="BF205" t="n">
         <v>0</v>
@@ -39960,13 +39960,13 @@
         <v>0.3</v>
       </c>
       <c r="BC207" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE207" t="n">
         <v>1.7</v>
-      </c>
-      <c r="BD207" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE207" t="n">
-        <v>0</v>
       </c>
       <c r="BF207" t="n">
         <v>0</v>
@@ -40139,13 +40139,13 @@
         <v>5.9</v>
       </c>
       <c r="BC208" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE208" t="n">
         <v>8.699999999999999</v>
-      </c>
-      <c r="BD208" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE208" t="n">
-        <v>0</v>
       </c>
       <c r="BF208" t="n">
         <v>0</v>
@@ -40318,13 +40318,13 @@
         <v>3.7</v>
       </c>
       <c r="BC209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE209" t="n">
         <v>2.9</v>
-      </c>
-      <c r="BD209" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE209" t="n">
-        <v>0</v>
       </c>
       <c r="BF209" t="n">
         <v>0</v>
@@ -40502,13 +40502,13 @@
         <v>3.6</v>
       </c>
       <c r="BC210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE210" t="n">
         <v>6</v>
-      </c>
-      <c r="BD210" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE210" t="n">
-        <v>3.6</v>
       </c>
       <c r="BF210" t="n">
         <v>0</v>
@@ -40681,10 +40681,10 @@
         <v>4.7</v>
       </c>
       <c r="BC211" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD211" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BE211" t="n">
         <v>0</v>
@@ -41042,13 +41042,13 @@
         <v>5.2</v>
       </c>
       <c r="BC213" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE213" t="n">
         <v>12.1</v>
-      </c>
-      <c r="BD213" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE213" t="n">
-        <v>0</v>
       </c>
       <c r="BF213" t="n">
         <v>0</v>
@@ -41516,13 +41516,13 @@
         <v>1.4</v>
       </c>
       <c r="BC216" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BD216" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="BE216" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BF216" t="n">
         <v>0</v>
@@ -41700,13 +41700,13 @@
         <v>0.2</v>
       </c>
       <c r="BC217" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE217" t="n">
         <v>42.9</v>
-      </c>
-      <c r="BD217" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE217" t="n">
-        <v>4.7</v>
       </c>
       <c r="BF217" t="n">
         <v>0</v>
@@ -41879,13 +41879,13 @@
         <v>0</v>
       </c>
       <c r="BC218" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE218" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BD218" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BE218" t="n">
-        <v>0</v>
       </c>
       <c r="BF218" t="n">
         <v>0</v>
@@ -42058,13 +42058,13 @@
         <v>4.3</v>
       </c>
       <c r="BC219" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BE219" t="n">
         <v>2.3</v>
-      </c>
-      <c r="BD219" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE219" t="n">
-        <v>0.8</v>
       </c>
       <c r="BF219" t="n">
         <v>0</v>
@@ -42237,10 +42237,10 @@
         <v>0.1</v>
       </c>
       <c r="BC220" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BD220" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="BE220" t="n">
         <v>0</v>
@@ -42416,13 +42416,13 @@
         <v>0</v>
       </c>
       <c r="BC221" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE221" t="n">
         <v>3.3</v>
-      </c>
-      <c r="BD221" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BE221" t="n">
-        <v>0</v>
       </c>
       <c r="BF221" t="n">
         <v>0</v>
@@ -42595,13 +42595,13 @@
         <v>0.6</v>
       </c>
       <c r="BC222" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE222" t="n">
         <v>61.8</v>
-      </c>
-      <c r="BD222" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE222" t="n">
-        <v>0.2</v>
       </c>
       <c r="BF222" t="n">
         <v>0</v>
@@ -42779,13 +42779,13 @@
         <v>5.5</v>
       </c>
       <c r="BC223" t="n">
-        <v>0</v>
+        <v>23.2</v>
       </c>
       <c r="BD223" t="n">
-        <v>23.2</v>
+        <v>4.2</v>
       </c>
       <c r="BE223" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BF223" t="n">
         <v>0</v>
@@ -42963,10 +42963,10 @@
         <v>0</v>
       </c>
       <c r="BC224" t="n">
-        <v>0</v>
+        <v>33.1</v>
       </c>
       <c r="BD224" t="n">
-        <v>33.1</v>
+        <v>0</v>
       </c>
       <c r="BE224" t="n">
         <v>0</v>
@@ -43142,13 +43142,13 @@
         <v>0</v>
       </c>
       <c r="BC225" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE225" t="n">
         <v>0.6</v>
-      </c>
-      <c r="BD225" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE225" t="n">
-        <v>0</v>
       </c>
       <c r="BF225" t="n">
         <v>0</v>
@@ -43326,13 +43326,13 @@
         <v>0</v>
       </c>
       <c r="BC226" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE226" t="n">
         <v>1.5</v>
-      </c>
-      <c r="BD226" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BE226" t="n">
-        <v>5.5</v>
       </c>
       <c r="BF226" t="n">
         <v>0</v>
@@ -43510,13 +43510,13 @@
         <v>9.9</v>
       </c>
       <c r="BC227" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE227" t="n">
         <v>1.1</v>
-      </c>
-      <c r="BD227" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BE227" t="n">
-        <v>3.8</v>
       </c>
       <c r="BF227" t="n">
         <v>0</v>
@@ -43694,13 +43694,13 @@
         <v>0</v>
       </c>
       <c r="BC228" t="n">
+        <v>57</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE228" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BD228" t="n">
-        <v>57</v>
-      </c>
-      <c r="BE228" t="n">
-        <v>0</v>
       </c>
       <c r="BF228" t="n">
         <v>0</v>
@@ -43881,13 +43881,13 @@
         <v>1.7</v>
       </c>
       <c r="BC229" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="BE229" t="n">
         <v>53.7</v>
-      </c>
-      <c r="BD229" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="BE229" t="n">
-        <v>51.4</v>
       </c>
       <c r="BF229" t="n">
         <v>0</v>
@@ -44068,13 +44068,13 @@
         <v>0</v>
       </c>
       <c r="BC230" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="BE230" t="n">
         <v>12.6</v>
-      </c>
-      <c r="BD230" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BE230" t="n">
-        <v>50.2</v>
       </c>
       <c r="BF230" t="n">
         <v>0</v>
@@ -44260,13 +44260,13 @@
         <v>0.8</v>
       </c>
       <c r="BC231" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="BE231" t="n">
         <v>16.5</v>
-      </c>
-      <c r="BD231" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE231" t="n">
-        <v>97.40000000000001</v>
       </c>
       <c r="BF231" t="n">
         <v>0</v>
@@ -44444,13 +44444,13 @@
         <v>0</v>
       </c>
       <c r="BC232" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD232" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="BE232" t="n">
         <v>3</v>
-      </c>
-      <c r="BD232" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE232" t="n">
-        <v>16.1</v>
       </c>
       <c r="BF232" t="n">
         <v>0</v>
@@ -44628,13 +44628,13 @@
         <v>0</v>
       </c>
       <c r="BC233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE233" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BD233" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE233" t="n">
-        <v>2.1</v>
       </c>
       <c r="BF233" t="n">
         <v>0</v>
@@ -44812,13 +44812,13 @@
         <v>0</v>
       </c>
       <c r="BC234" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BD234" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE234" t="n">
         <v>11</v>
-      </c>
-      <c r="BD234" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BE234" t="n">
-        <v>3.5</v>
       </c>
       <c r="BF234" t="n">
         <v>0</v>
@@ -44999,10 +44999,10 @@
         <v>0</v>
       </c>
       <c r="BD235" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BE235" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BF235" t="n">
         <v>0</v>
@@ -45178,10 +45178,10 @@
         <v>0</v>
       </c>
       <c r="BD236" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="BE236" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="BF236" t="n">
         <v>0</v>
@@ -45359,13 +45359,13 @@
         <v>0</v>
       </c>
       <c r="BC237" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BD237" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE237" t="n">
         <v>0.6</v>
-      </c>
-      <c r="BD237" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BE237" t="n">
-        <v>3.4</v>
       </c>
       <c r="BF237" t="n">
         <v>0</v>
@@ -45722,13 +45722,13 @@
         <v>0</v>
       </c>
       <c r="BC239" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE239" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BD239" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE239" t="n">
-        <v>0</v>
       </c>
       <c r="BF239" t="n">
         <v>0</v>
@@ -45908,13 +45908,13 @@
         <v>6.6</v>
       </c>
       <c r="BC240" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE240" t="n">
         <v>31.2</v>
-      </c>
-      <c r="BD240" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE240" t="n">
-        <v>0.2</v>
       </c>
       <c r="BF240" t="n">
         <v>0</v>
@@ -46093,10 +46093,10 @@
         <v>3.7</v>
       </c>
       <c r="BC241" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="BD241" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="BE241" t="n">
         <v>0</v>
@@ -46286,13 +46286,13 @@
         <v>0</v>
       </c>
       <c r="BC242" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD242" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE242" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BD242" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE242" t="n">
-        <v>0</v>
       </c>
       <c r="BF242" t="n">
         <v>0</v>
@@ -46479,13 +46479,13 @@
         <v>0</v>
       </c>
       <c r="BC243" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD243" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE243" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD243" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE243" t="n">
-        <v>0</v>
       </c>
       <c r="BF243" t="n">
         <v>0.2</v>
@@ -46873,13 +46873,13 @@
         <v>6.3</v>
       </c>
       <c r="BC245" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BD245" t="n">
-        <v>0.1</v>
+        <v>51.4</v>
       </c>
       <c r="BE245" t="n">
-        <v>51.4</v>
+        <v>0</v>
       </c>
       <c r="BF245" t="n">
         <v>0</v>
@@ -47069,13 +47069,13 @@
         <v>0</v>
       </c>
       <c r="BC246" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD246" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE246" t="n">
         <v>49.7</v>
-      </c>
-      <c r="BD246" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE246" t="n">
-        <v>0</v>
       </c>
       <c r="BF246" t="n">
         <v>0</v>
@@ -47262,13 +47262,13 @@
         <v>0</v>
       </c>
       <c r="BC247" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD247" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE247" t="n">
         <v>68.7</v>
-      </c>
-      <c r="BD247" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE247" t="n">
-        <v>0</v>
       </c>
       <c r="BF247" t="n">
         <v>0</v>
@@ -47443,13 +47443,13 @@
         <v>4.3</v>
       </c>
       <c r="BC248" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD248" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE248" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BD248" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE248" t="n">
-        <v>0.2</v>
       </c>
       <c r="BF248" t="n">
         <v>0</v>
@@ -48372,13 +48372,13 @@
         <v>0</v>
       </c>
       <c r="BC253" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD253" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE253" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD253" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE253" t="n">
-        <v>0</v>
       </c>
       <c r="BF253" t="n">
         <v>0</v>
@@ -48570,13 +48570,13 @@
         <v>1.5</v>
       </c>
       <c r="BC254" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD254" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE254" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BD254" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE254" t="n">
-        <v>3.4</v>
       </c>
       <c r="BF254" t="n">
         <v>0</v>
@@ -48766,13 +48766,13 @@
         <v>0</v>
       </c>
       <c r="BC255" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BD255" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BE255" t="n">
         <v>49.6</v>
-      </c>
-      <c r="BD255" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BE255" t="n">
-        <v>1.9</v>
       </c>
       <c r="BF255" t="n">
         <v>0</v>
@@ -48964,13 +48964,13 @@
         <v>0.7</v>
       </c>
       <c r="BC256" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD256" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE256" t="n">
         <v>46.2</v>
-      </c>
-      <c r="BD256" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE256" t="n">
-        <v>2.9</v>
       </c>
       <c r="BF256" t="n">
         <v>0</v>
@@ -49165,13 +49165,13 @@
         <v>0</v>
       </c>
       <c r="BC257" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD257" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE257" t="n">
         <v>11.9</v>
-      </c>
-      <c r="BD257" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BE257" t="n">
-        <v>4.6</v>
       </c>
       <c r="BF257" t="n">
         <v>0</v>
@@ -49358,13 +49358,13 @@
         <v>0</v>
       </c>
       <c r="BC258" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD258" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE258" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BD258" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE258" t="n">
-        <v>0</v>
       </c>
       <c r="BF258" t="n">
         <v>0</v>
@@ -49561,13 +49561,13 @@
         <v>4.9</v>
       </c>
       <c r="BC259" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="BD259" t="n">
+        <v>173</v>
+      </c>
+      <c r="BE259" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BD259" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="BE259" t="n">
-        <v>173</v>
       </c>
       <c r="BF259" t="n">
         <v>0</v>
@@ -49922,10 +49922,10 @@
         <v>0</v>
       </c>
       <c r="BD261" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE261" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BF261" t="n">
         <v>0</v>
@@ -50100,13 +50100,13 @@
         <v>0.2</v>
       </c>
       <c r="BC262" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD262" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE262" t="n">
         <v>20.8</v>
-      </c>
-      <c r="BD262" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE262" t="n">
-        <v>0</v>
       </c>
       <c r="BF262" t="n">
         <v>0</v>
@@ -50293,13 +50293,13 @@
         <v>5.7</v>
       </c>
       <c r="BC263" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="BD263" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="BE263" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="BF263" t="n">
         <v>0</v>
@@ -50486,13 +50486,13 @@
         <v>1.8</v>
       </c>
       <c r="BC264" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD264" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BE264" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD264" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE264" t="n">
-        <v>0.5</v>
       </c>
       <c r="BF264" t="n">
         <v>0</v>
@@ -50682,13 +50682,13 @@
         <v>2.8</v>
       </c>
       <c r="BC265" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD265" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE265" t="n">
         <v>10.4</v>
-      </c>
-      <c r="BD265" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE265" t="n">
-        <v>0</v>
       </c>
       <c r="BF265" t="n">
         <v>0</v>
@@ -50875,13 +50875,13 @@
         <v>0</v>
       </c>
       <c r="BC266" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE266" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD266" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE266" t="n">
-        <v>0</v>
       </c>
       <c r="BF266" t="n">
         <v>0</v>
@@ -51068,13 +51068,13 @@
         <v>0</v>
       </c>
       <c r="BC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE267" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BD267" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE267" t="n">
-        <v>0</v>
       </c>
       <c r="BF267" t="n">
         <v>0</v>
@@ -51252,13 +51252,13 @@
         <v>0</v>
       </c>
       <c r="BC268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE268" t="n">
         <v>0.3</v>
-      </c>
-      <c r="BD268" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE268" t="n">
-        <v>0</v>
       </c>
       <c r="BF268" t="n">
         <v>0</v>
@@ -51436,13 +51436,13 @@
         <v>6.4</v>
       </c>
       <c r="BC269" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE269" t="n">
         <v>12.6</v>
-      </c>
-      <c r="BD269" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BE269" t="n">
-        <v>3</v>
       </c>
       <c r="BF269" t="n">
         <v>0</v>
@@ -51617,13 +51617,13 @@
         <v>0</v>
       </c>
       <c r="BC270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE270" t="n">
         <v>6.9</v>
-      </c>
-      <c r="BD270" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE270" t="n">
-        <v>0</v>
       </c>
       <c r="BF270" t="n">
         <v>0</v>
@@ -52154,13 +52154,13 @@
         <v>2.2</v>
       </c>
       <c r="BC273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE273" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD273" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE273" t="n">
-        <v>0</v>
       </c>
       <c r="BF273" t="n">
         <v>0</v>
@@ -52347,13 +52347,13 @@
         <v>0</v>
       </c>
       <c r="BC274" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD274" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE274" t="n">
         <v>0.4</v>
-      </c>
-      <c r="BD274" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE274" t="n">
-        <v>0</v>
       </c>
       <c r="BF274" t="n">
         <v>0</v>
@@ -52540,10 +52540,10 @@
         <v>0.6</v>
       </c>
       <c r="BD275" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BE275" t="n">
         <v>0.6</v>
-      </c>
-      <c r="BE275" t="n">
-        <v>8.1</v>
       </c>
       <c r="BF275" t="n">
         <v>0</v>
@@ -52730,13 +52730,13 @@
         <v>0</v>
       </c>
       <c r="BC276" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD276" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE276" t="n">
         <v>1.4</v>
-      </c>
-      <c r="BD276" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE276" t="n">
-        <v>0</v>
       </c>
       <c r="BF276" t="n">
         <v>0</v>
@@ -52928,13 +52928,13 @@
         <v>0</v>
       </c>
       <c r="BC277" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD277" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="BE277" t="n">
         <v>18.2</v>
-      </c>
-      <c r="BD277" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE277" t="n">
-        <v>11.7</v>
       </c>
       <c r="BF277" t="n">
         <v>0</v>
@@ -53129,13 +53129,13 @@
         <v>0.1</v>
       </c>
       <c r="BC278" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD278" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="BE278" t="n">
         <v>12.2</v>
-      </c>
-      <c r="BD278" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BE278" t="n">
-        <v>11.7</v>
       </c>
       <c r="BF278" t="n">
         <v>0</v>
@@ -53340,13 +53340,13 @@
         <v>7.3</v>
       </c>
       <c r="BC279" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="BD279" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BE279" t="n">
         <v>298.2</v>
-      </c>
-      <c r="BD279" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="BE279" t="n">
-        <v>92.40000000000001</v>
       </c>
       <c r="BF279" t="n">
         <v>0</v>
@@ -53541,13 +53541,13 @@
         <v>13</v>
       </c>
       <c r="BC280" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="BD280" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="BE280" t="n">
         <v>302.6</v>
-      </c>
-      <c r="BD280" t="n">
-        <v>144.5</v>
-      </c>
-      <c r="BE280" t="n">
-        <v>385.3</v>
       </c>
       <c r="BF280" t="n">
         <v>0</v>
@@ -53732,13 +53732,13 @@
         <v>0</v>
       </c>
       <c r="BC281" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BD281" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BE281" t="n">
         <v>72.2</v>
-      </c>
-      <c r="BD281" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="BE281" t="n">
-        <v>69.90000000000001</v>
       </c>
       <c r="BF281" t="n">
         <v>0</v>
@@ -53933,13 +53933,13 @@
         <v>0.9</v>
       </c>
       <c r="BC282" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD282" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE282" t="n">
         <v>11.9</v>
-      </c>
-      <c r="BD282" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE282" t="n">
-        <v>1.6</v>
       </c>
       <c r="BF282" t="n">
         <v>0</v>
@@ -54114,13 +54114,13 @@
         <v>1.8</v>
       </c>
       <c r="BC283" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD283" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE283" t="n">
         <v>3.7</v>
-      </c>
-      <c r="BD283" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BE283" t="n">
-        <v>1.4</v>
       </c>
       <c r="BF283" t="n">
         <v>0</v>
@@ -54306,13 +54306,13 @@
         <v>0.3</v>
       </c>
       <c r="BC284" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD284" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE284" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BD284" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE284" t="n">
-        <v>0</v>
       </c>
       <c r="BF284" t="n">
         <v>0</v>
@@ -54490,13 +54490,13 @@
         <v>0.3</v>
       </c>
       <c r="BC285" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD285" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE285" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BD285" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE285" t="n">
-        <v>0</v>
       </c>
       <c r="BF285" t="n">
         <v>0</v>
@@ -54685,13 +54685,13 @@
         <v>4.1</v>
       </c>
       <c r="BC286" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="BD286" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE286" t="n">
         <v>34.6</v>
-      </c>
-      <c r="BD286" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="BE286" t="n">
-        <v>3.9</v>
       </c>
       <c r="BF286" t="n">
         <v>0</v>
@@ -54876,13 +54876,13 @@
         <v>4.4</v>
       </c>
       <c r="BC287" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD287" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="BE287" t="n">
         <v>56.2</v>
-      </c>
-      <c r="BD287" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE287" t="n">
-        <v>11.4</v>
       </c>
       <c r="BF287" t="n">
         <v>0</v>
@@ -55267,10 +55267,10 @@
         <v>0.9</v>
       </c>
       <c r="BC289" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="BD289" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="BE289" t="n">
         <v>0</v>
@@ -55464,13 +55464,13 @@
         <v>173</v>
       </c>
       <c r="BC290" t="n">
+        <v>399.7</v>
+      </c>
+      <c r="BD290" t="n">
+        <v>3912</v>
+      </c>
+      <c r="BE290" t="n">
         <v>37.9</v>
-      </c>
-      <c r="BD290" t="n">
-        <v>399.7</v>
-      </c>
-      <c r="BE290" t="n">
-        <v>3912</v>
       </c>
       <c r="BF290" t="n">
         <v>13.9</v>
@@ -55661,13 +55661,13 @@
         <v>2.8</v>
       </c>
       <c r="BC291" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="BD291" t="n">
-        <v>0.7</v>
+        <v>949</v>
       </c>
       <c r="BE291" t="n">
-        <v>949</v>
+        <v>0</v>
       </c>
       <c r="BF291" t="n">
         <v>0</v>
@@ -55855,13 +55855,13 @@
         <v>15.5</v>
       </c>
       <c r="BC292" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="BD292" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="BE292" t="n">
         <v>356.6</v>
-      </c>
-      <c r="BD292" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="BE292" t="n">
-        <v>32.6</v>
       </c>
       <c r="BF292" t="n">
         <v>0.2</v>
@@ -56066,13 +56066,13 @@
         <v>48.8</v>
       </c>
       <c r="BC293" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="BD293" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="BE293" t="n">
         <v>40.3</v>
-      </c>
-      <c r="BD293" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="BE293" t="n">
-        <v>45.4</v>
       </c>
       <c r="BF293" t="n">
         <v>0</v>
@@ -56261,13 +56261,13 @@
         <v>26.4</v>
       </c>
       <c r="BC294" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BD294" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="BE294" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BD294" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BE294" t="n">
-        <v>65.40000000000001</v>
       </c>
       <c r="BF294" t="n">
         <v>0</v>
@@ -56459,13 +56459,13 @@
         <v>4</v>
       </c>
       <c r="BC295" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="BD295" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BE295" t="n">
         <v>0.7</v>
-      </c>
-      <c r="BD295" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="BE295" t="n">
-        <v>6.9</v>
       </c>
       <c r="BF295" t="n">
         <v>0</v>
@@ -56652,13 +56652,13 @@
         <v>0</v>
       </c>
       <c r="BC296" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD296" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE296" t="n">
         <v>19.8</v>
-      </c>
-      <c r="BD296" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE296" t="n">
-        <v>0</v>
       </c>
       <c r="BF296" t="n">
         <v>0</v>
@@ -56841,13 +56841,13 @@
         <v>0</v>
       </c>
       <c r="BC297" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BD297" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BE297" t="n">
         <v>6.9</v>
-      </c>
-      <c r="BD297" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BE297" t="n">
-        <v>0.8</v>
       </c>
       <c r="BF297" t="n">
         <v>0</v>
@@ -57236,13 +57236,13 @@
         <v>17.3</v>
       </c>
       <c r="BC299" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BD299" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE299" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BD299" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="BE299" t="n">
-        <v>2.4</v>
       </c>
       <c r="BF299" t="n">
         <v>0</v>
@@ -57428,10 +57428,10 @@
         <v>0.2</v>
       </c>
       <c r="BC300" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="BD300" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="BE300" t="n">
         <v>0</v>
@@ -57623,13 +57623,13 @@
         <v>15.7</v>
       </c>
       <c r="BC301" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="BD301" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE301" t="n">
         <v>3.1</v>
-      </c>
-      <c r="BD301" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="BE301" t="n">
-        <v>2.6</v>
       </c>
       <c r="BF301" t="n">
         <v>0.4</v>
@@ -58171,13 +58171,13 @@
         <v>0.1</v>
       </c>
       <c r="BC304" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD304" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE304" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BD304" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE304" t="n">
-        <v>0</v>
       </c>
       <c r="BF304" t="n">
         <v>0</v>
@@ -58358,13 +58358,13 @@
         <v>0</v>
       </c>
       <c r="BC305" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD305" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE305" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD305" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE305" t="n">
-        <v>0</v>
       </c>
       <c r="BF305" t="n">
         <v>0</v>
@@ -59052,13 +59052,13 @@
         <v>0</v>
       </c>
       <c r="BC309" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD309" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE309" t="n">
         <v>0.2</v>
-      </c>
-      <c r="BD309" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE309" t="n">
-        <v>0</v>
       </c>
       <c r="BF309" t="n">
         <v>0</v>
@@ -59231,13 +59231,13 @@
         <v>0</v>
       </c>
       <c r="BC310" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD310" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE310" t="n">
         <v>1.5</v>
-      </c>
-      <c r="BD310" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE310" t="n">
-        <v>0</v>
       </c>
       <c r="BF310" t="n">
         <v>0</v>
@@ -59410,13 +59410,13 @@
         <v>0.5</v>
       </c>
       <c r="BC311" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD311" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE311" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD311" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE311" t="n">
-        <v>0</v>
       </c>
       <c r="BF311" t="n">
         <v>0</v>
@@ -59961,13 +59961,13 @@
         <v>2.9</v>
       </c>
       <c r="BC314" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD314" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE314" t="n">
         <v>0.6</v>
-      </c>
-      <c r="BD314" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE314" t="n">
-        <v>0</v>
       </c>
       <c r="BF314" t="n">
         <v>0</v>
@@ -60143,13 +60143,13 @@
         <v>0.1</v>
       </c>
       <c r="BC315" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD315" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE315" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD315" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE315" t="n">
-        <v>0</v>
       </c>
       <c r="BF315" t="n">
         <v>0</v>
@@ -60325,13 +60325,13 @@
         <v>2</v>
       </c>
       <c r="BC316" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD316" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE316" t="n">
         <v>0.6</v>
-      </c>
-      <c r="BD316" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE316" t="n">
-        <v>0</v>
       </c>
       <c r="BF316" t="n">
         <v>0</v>
@@ -60881,13 +60881,13 @@
         <v>0</v>
       </c>
       <c r="BC319" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD319" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE319" t="n">
         <v>0.3</v>
-      </c>
-      <c r="BD319" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE319" t="n">
-        <v>0</v>
       </c>
       <c r="BF319" t="n">
         <v>0</v>
@@ -61385,13 +61385,13 @@
         <v>0</v>
       </c>
       <c r="BC322" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD322" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE322" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD322" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE322" t="n">
-        <v>0</v>
       </c>
       <c r="BF322" t="n">
         <v>0</v>
@@ -61578,13 +61578,13 @@
         <v>0</v>
       </c>
       <c r="BC323" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD323" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE323" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD323" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE323" t="n">
-        <v>0</v>
       </c>
       <c r="BF323" t="n">
         <v>0</v>
@@ -61768,13 +61768,13 @@
         <v>0.7</v>
       </c>
       <c r="BC324" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD324" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="BE324" t="n">
         <v>0.4</v>
-      </c>
-      <c r="BD324" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE324" t="n">
-        <v>22.3</v>
       </c>
       <c r="BF324" t="n">
         <v>0</v>
@@ -61971,13 +61971,13 @@
         <v>15.7</v>
       </c>
       <c r="BC325" t="n">
+        <v>102</v>
+      </c>
+      <c r="BD325" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="BE325" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BD325" t="n">
-        <v>102</v>
-      </c>
-      <c r="BE325" t="n">
-        <v>84.09999999999999</v>
       </c>
       <c r="BF325" t="n">
         <v>0</v>
@@ -62164,13 +62164,13 @@
         <v>3.6</v>
       </c>
       <c r="BC326" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE326" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BD326" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE326" t="n">
-        <v>0</v>
       </c>
       <c r="BF326" t="n">
         <v>0</v>
@@ -62549,13 +62549,13 @@
         <v>0</v>
       </c>
       <c r="BC328" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD328" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE328" t="n">
         <v>1.5</v>
-      </c>
-      <c r="BD328" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE328" t="n">
-        <v>0</v>
       </c>
       <c r="BF328" t="n">
         <v>0</v>
@@ -63374,7 +63374,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>comfort_km_most</t>
+          <t>comfort_km_c1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -63384,14 +63384,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Classified length in comfort class MOST.</t>
+          <t>Classified length in traffic comfort class C1 (separated paths, or slow streets with few cars).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>comfort_km_some</t>
+          <t>comfort_km_c2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -63401,14 +63401,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Classified length in comfort class SOME.</t>
+          <t>Classified length in traffic comfort class C2 (sharing light traffic, or bike lanes on calm roads).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>comfort_km_few</t>
+          <t>comfort_km_c3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -63418,14 +63418,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Classified length in comfort class FEW.</t>
+          <t>Classified length in traffic comfort class C3 (sharing busier traffic, or bike lanes on busy roads).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>comfort_km_very_few</t>
+          <t>comfort_km_c4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -63435,14 +63435,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Classified length in comfort class VERY FEW.</t>
+          <t>Classified length in traffic comfort class C4 (fast or heavy traffic, a painted line at most).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>comfort_km_backcountry</t>
+          <t>comfort_km_c5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -63452,14 +63452,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Classified length in comfort class BACKCOUNTRY.</t>
+          <t>Classified length in traffic comfort class C5 (highway-speed traffic, 60+ km/h, a painted line at most).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>comfort_km_experienced_only</t>
+          <t>comfort_km_c6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -63469,14 +63469,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Classified length in comfort class EXPERIENCED ONLY.</t>
+          <t>Classified length in traffic comfort class C6 (fast highway traffic, 70+ km/h, a painted line at most).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>comfort_km_risk</t>
+          <t>comfort_km_backcountry</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -63486,7 +63486,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Classified length in comfort class RISK.</t>
+          <t>Classified length in traffic comfort class BACKCOUNTRY (bare track, beyond traffic data; off the ladder).</t>
         </is>
       </c>
     </row>
@@ -63503,7 +63503,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Classified length in comfort class FORBIDDEN.</t>
+          <t>Classified length in traffic comfort class FORBIDDEN (cycling not permitted; off the ladder).</t>
         </is>
       </c>
     </row>

--- a/research/files/route_metrics.xlsx
+++ b/research/files/route_metrics.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Published 2026-08-09 by BC Cycle Tourism Society.</t>
+          <t>Published 2026-09-02 by BC Cycle Tourism Society.</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Suggested citation: BC Cycle Tourism Society (2026). Published BC cycling routes — derived metrics [data set]. Version 2026-08-09. https://bccycletourism.ca/research/</t>
+          <t>Suggested citation: BC Cycle Tourism Society (2026). Published BC cycling routes — derived metrics [data set]. Version 2026-09-02. https://bccycletourism.ca/research/</t>
         </is>
       </c>
     </row>
